--- a/results/Int Task Remove ACC -1.0/Rando_fi_explain.xlsx
+++ b/results/Int Task Remove ACC -1.0/Rando_fi_explain.xlsx
@@ -1148,268 +1148,268 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0002413847520902478</v>
+        <v>-0.00312353474495615</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.001296230224461912</v>
+        <v>-0.002811252400143262</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.000409489331889281</v>
+        <v>-0.000444279841263543</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001801482605839259</v>
+        <v>0.001530354447028592</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001208928849399844</v>
+        <v>-0.002585648109155015</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0004286152102244155</v>
+        <v>0.000593400624302962</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001461395309463587</v>
+        <v>3.578162920072292e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.366197488194102e-05</v>
+        <v>-0.002345904279780792</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01374031265239412</v>
+        <v>0.01524715885037058</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01737780159040911</v>
+        <v>0.0165636302293345</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.003539570325152256</v>
+        <v>-0.00196686570131729</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0002482258859181838</v>
+        <v>-0.00202380775121839</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001602401386565405</v>
+        <v>0.0008282528980357972</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003237883083110512</v>
+        <v>0.005494790136821332</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.006772627285362841</v>
+        <v>0.009920271955223693</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0009818501683871196</v>
+        <v>5.097149469269688e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0002739305837391137</v>
+        <v>0.0009488641468138705</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0006178533158901679</v>
+        <v>-0.0003600007677582772</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0006383210518874471</v>
+        <v>-0.001735624392446546</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0002108974198357383</v>
+        <v>0.000124918488486988</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0001413169476588847</v>
+        <v>0.000851588551355258</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.002204971054884525</v>
+        <v>-0.001550692674000117</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0009946483277211405</v>
+        <v>0.000461865691615485</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.000595013920130173</v>
+        <v>0.001068984067487443</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001412446230921513</v>
+        <v>0.002092422864083912</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0002280190735980292</v>
+        <v>-5.843027861436312e-05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.006233827174551915</v>
+        <v>0.004319205908781563</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.004090026349326483</v>
+        <v>-0.003925230776215637</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.001338996516084919</v>
+        <v>-0.001451056594944021</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.002017217068470661</v>
+        <v>-0.005272553043818265</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.28527175373139e-05</v>
+        <v>0.0001919024939140146</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0001769194397814045</v>
+        <v>6.095768124603774e-05</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.002873357935324851</v>
+        <v>-0.004873390786181886</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.003931884038426882</v>
+        <v>-0.002468660243375536</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.0005757688925728377</v>
+        <v>-0.001023097695425993</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.0002239738739655683</v>
+        <v>0.0002375853451426191</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.00201441671265295</v>
+        <v>0.002063092569560997</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.00269423221363396</v>
+        <v>-0.002022812476129751</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.000537500147057347</v>
+        <v>6.847298753641205e-05</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.002189247009751233</v>
+        <v>0.00223568794438538</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.003015772601972166</v>
+        <v>-0.003244212707837415</v>
       </c>
       <c r="AS3" t="n">
-        <v>-7.679987339412335e-05</v>
+        <v>0.0003633816150808955</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.005523215148532258</v>
+        <v>-0.00369480162189879</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.00145588273023151</v>
+        <v>0.001642462528067808</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.0007831602457928921</v>
+        <v>-0.0001189053527983087</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.0004869423823957409</v>
+        <v>-0.0005033202960025296</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0002762326004663618</v>
+        <v>0.0002007850437215476</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.0003331867690910673</v>
+        <v>0.0001029080813611349</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.0005761838636254713</v>
+        <v>-0.001995279455451411</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.00329269606126749</v>
+        <v>-0.003789878461014362</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.008157730902209361</v>
+        <v>-0.002386737051864133</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.525497140673739e-05</v>
+        <v>-0.0005445297857051635</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.0003628795579953069</v>
+        <v>2.818312364506455e-06</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.0001117058399457471</v>
+        <v>-0.0001330738681220556</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.003432508613480374</v>
+        <v>-0.003959336569505229</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.001681043966870495</v>
+        <v>-0.002135117284317248</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>5.918910920390541e-06</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.0004321392562368608</v>
+        <v>1.141198569228452e-05</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.0008343432755202055</v>
+        <v>6.041447441875738e-05</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.002512072058829262</v>
+        <v>-0.0008520981656689397</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.0001204780405144246</v>
+        <v>-0.0005354077937613156</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.001140316294716271</v>
+        <v>0.0001841595105991278</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.006295617779040872</v>
+        <v>-0.002303106358068654</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.0005877567758222189</v>
+        <v>-8.041177889625423e-05</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.0001415037128800646</v>
+        <v>0.0006500693066099383</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0002766288665031635</v>
+        <v>-2.174188827560263e-05</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0009117220112382152</v>
+        <v>3.598743092473891e-05</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0009398347466626353</v>
+        <v>2.560839382207529e-05</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0.0001631770305361824</v>
+        <v>-0.0002772333296634921</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.005626051638261153</v>
+        <v>0.004449941057732649</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.0006324770556494064</v>
+        <v>6.318518405623809e-05</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.00241620908431252</v>
+        <v>0.00101428487651594</v>
       </c>
       <c r="BX3" t="n">
-        <v>9.897035744910964e-05</v>
+        <v>-3.924661026364018e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.0005856792059697058</v>
+        <v>0.0002239371843982118</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.376947057294967e-05</v>
+        <v>-4.179801246970484e-05</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.15240564678798e-05</v>
+        <v>1.178897730622186e-05</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0006271663325208498</v>
+        <v>0.0005886712318649213</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.0009159097096337963</v>
+        <v>-0.0004772663598801719</v>
       </c>
       <c r="CD3" t="n">
-        <v>-2.938559193184087e-06</v>
+        <v>-5.921461467217504e-05</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.0001444823464047229</v>
+        <v>0.0001700440833823902</v>
       </c>
       <c r="CF3" t="n">
-        <v>-7.519913082107417e-05</v>
+        <v>-0.0005534704533734613</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.0004147690339796141</v>
+        <v>0.0005540927439729315</v>
       </c>
       <c r="CH3" t="n">
-        <v>9.193812875004418e-05</v>
+        <v>-0.0006247556379092589</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.0004750725724164617</v>
+        <v>9.769673697695323e-05</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.00113918194203626</v>
+        <v>0.0002555392293816384</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.0005344653132388321</v>
+        <v>0.0003938796741524808</v>
       </c>
     </row>
     <row r="4">
@@ -1419,268 +1419,268 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005293099548079733</v>
+        <v>0.00421561077523431</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006228702673296586</v>
+        <v>0.005960997027934421</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007745813600571403</v>
+        <v>0.005002231033595812</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003384622376849243</v>
+        <v>0.003418120746150934</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005073437210211584</v>
+        <v>0.006550758512667919</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004257540225172047</v>
+        <v>0.004994395386754455</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002176125730600953</v>
+        <v>0.0003529909398978922</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005039594306702524</v>
+        <v>0.005320850886139159</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01102418589576935</v>
+        <v>0.01330732262084007</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0116698769484104</v>
+        <v>0.01214972207099673</v>
       </c>
       <c r="M4" t="n">
-        <v>0.005077023821248442</v>
+        <v>0.007875754731667822</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007396027845889998</v>
+        <v>0.007440533437787745</v>
       </c>
       <c r="O4" t="n">
-        <v>0.008528403122001399</v>
+        <v>0.006198380241055482</v>
       </c>
       <c r="P4" t="n">
-        <v>0.009785973405029623</v>
+        <v>0.01606171835449482</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.008098742384474011</v>
+        <v>0.01114873890554219</v>
       </c>
       <c r="R4" t="n">
-        <v>0.003545154030670602</v>
+        <v>0.003742747541612683</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003889392279898747</v>
+        <v>0.003967270431905292</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00500097140256815</v>
+        <v>0.003646803997853926</v>
       </c>
       <c r="U4" t="n">
-        <v>0.003724057982079892</v>
+        <v>0.004525050480664891</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0002058770652567016</v>
+        <v>0.0002730126189958911</v>
       </c>
       <c r="W4" t="n">
-        <v>0.008299533981495104</v>
+        <v>0.01166547154712053</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004306929189904087</v>
+        <v>0.005116529851720493</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002068844063721298</v>
+        <v>0.003554164838112641</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00183933191698399</v>
+        <v>0.001876050057475101</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002281799889609012</v>
+        <v>0.003709525070474328</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001017932393698226</v>
+        <v>0.001059045172000391</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.005559672256596356</v>
+        <v>0.005028469863067293</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.007604286977822159</v>
+        <v>0.01129243654825293</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.002649617617921589</v>
+        <v>0.0062831942837558</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.006677377364122568</v>
+        <v>0.008086890697691421</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001006331900340771</v>
+        <v>0.000775885608044726</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0007073176818211622</v>
+        <v>0.0006477402652163341</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.006869056699081686</v>
+        <v>0.008319160674018876</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.007552994592826644</v>
+        <v>0.008146472804258741</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0005861622869276849</v>
+        <v>0.001275472642143497</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.001339219906858557</v>
+        <v>0.001353631001593908</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.002852664049827583</v>
+        <v>0.003862849319682387</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.003309248556163611</v>
+        <v>0.004229023936240845</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001140843561606773</v>
+        <v>0.001098655625709671</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.003437049538935889</v>
+        <v>0.003065541405810712</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.004458220152020948</v>
+        <v>0.006135959920650296</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.001619577145519544</v>
+        <v>0.003225402926187286</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.008261434552333413</v>
+        <v>0.005307806862859488</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.003872296972845221</v>
+        <v>0.006498115917896903</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.003490391249621563</v>
+        <v>0.003459518317733832</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.003831894919497814</v>
+        <v>0.004069417900448451</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.001097581360676281</v>
+        <v>0.0009579159528089683</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.002420156088810865</v>
+        <v>0.004221733539648735</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.01149123092012353</v>
+        <v>0.0083039621974634</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.01020958406943194</v>
+        <v>0.007143671574726035</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.01266349299027761</v>
+        <v>0.00615168516875009</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.001057736234710044</v>
+        <v>0.0009108870461894635</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0009717122974749124</v>
+        <v>0.0005759607288710255</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.0003188924180342831</v>
+        <v>0.001194633952852735</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.008247905542374871</v>
+        <v>0.009516967867914417</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.01128024302411333</v>
+        <v>0.004909165931244298</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1.871723977607767e-05</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0008310612988414624</v>
+        <v>0.0007755033269706688</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.004177814655412507</v>
+        <v>0.003124110284871634</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.007612520562873324</v>
+        <v>0.0039580757481611</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0005584065009154022</v>
+        <v>0.0006444757992738493</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.00327864843226165</v>
+        <v>0.003955708536281158</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.01166772397570153</v>
+        <v>0.006689238610205549</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.00399134163313853</v>
+        <v>0.005220210642305113</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.004746180341174314</v>
+        <v>0.003979890783074362</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0009360888276668633</v>
+        <v>0.0006557287697760378</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.003628477389781186</v>
+        <v>0.004009832510771153</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.002476248298450722</v>
+        <v>0.003274687027769362</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001075771272011826</v>
+        <v>0.001345519165087975</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.007094344396322739</v>
+        <v>0.005232879263003435</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.0025806967946619</v>
+        <v>0.00270577677783355</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.004174646704651487</v>
+        <v>0.005932553554373908</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0002161582736109839</v>
+        <v>0.0002401570839287683</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.001234228476822779</v>
+        <v>0.001546924095263832</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.001613886697423766</v>
+        <v>0.0007886641639971731</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.64422663228952e-05</v>
+        <v>3.728001957169739e-05</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.002433967760542855</v>
+        <v>0.001363463655923724</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.003396884444868367</v>
+        <v>0.003244678001716155</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.2767758216187e-05</v>
+        <v>0.000117520788360789</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.0006240883455610852</v>
+        <v>0.001031006319566442</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.001721297245165023</v>
+        <v>0.004025113301305137</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.003563779681390051</v>
+        <v>0.003857030159678824</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001283776211167722</v>
+        <v>0.001197963543462765</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.002821067172286077</v>
+        <v>0.004602109862887688</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.004462229966587742</v>
+        <v>0.002671422221832483</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.002250430649188203</v>
+        <v>0.001446477027297424</v>
       </c>
     </row>
     <row r="5">
@@ -1690,268 +1690,268 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.00608424336973481</v>
+        <v>-0.008297320656871254</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.01126476519734943</v>
+        <v>-0.01256122154998563</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01071737251512529</v>
+        <v>-0.008470181503889406</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.003102475712942621</v>
+        <v>-0.00577264653641203</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0100259291270527</v>
+        <v>-0.01946328516661747</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.004361921603300967</v>
+        <v>-0.005703541209652163</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0001872074882995567</v>
+        <v>-0.0005353955978584124</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.01086441681468326</v>
+        <v>-0.01366614664586586</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002099655280476387</v>
+        <v>-0.008758282915586335</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.001757418611351158</v>
+        <v>-0.005733218092768677</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.01391529818496108</v>
+        <v>-0.01465364120781524</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.007145085803432161</v>
+        <v>-0.01734370498415445</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.008153269951022734</v>
+        <v>-0.007519500780031219</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.00962258715067702</v>
+        <v>-0.01557134399052691</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.00952521380123863</v>
+        <v>-0.004452963727513959</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.003669724770642135</v>
+        <v>-0.004982764023816988</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.006677067082683341</v>
+        <v>-0.003687698069720558</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.008644168146832443</v>
+        <v>-0.008851391355831817</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.006038072575847686</v>
+        <v>-0.009235569422776924</v>
       </c>
       <c r="V5" t="n">
-        <v>-8.878366380585812e-05</v>
+        <v>-0.0005327483547477252</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01441202475685239</v>
+        <v>-0.01492007104795731</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.01261420571765406</v>
+        <v>-0.01316692667706711</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.002219591595146453</v>
+        <v>-0.00574102964118568</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.002933985330073374</v>
+        <v>-0.001598105948505491</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.001803178484107626</v>
+        <v>-0.005085803432137326</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.0008923259964306763</v>
+        <v>-0.001619804400977953</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0002959455460195826</v>
+        <v>0.001149425287356365</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.02238010657193606</v>
+        <v>-0.03060982830076963</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.004696053010659717</v>
+        <v>-0.01391355831853163</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.01950446557188127</v>
+        <v>-0.01971918876755071</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.001642178046672416</v>
+        <v>-0.001248049921996908</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.001279000594883983</v>
+        <v>-0.0008557457212713393</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.01682512244309995</v>
+        <v>-0.02527301092043683</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.02101835405565422</v>
+        <v>-0.02072232089994074</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.001933372992266491</v>
+        <v>-0.003331350386674614</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.002564102564102622</v>
+        <v>-0.002516281823564193</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.002506112469437682</v>
+        <v>-0.002883108743340657</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.008465770171149167</v>
+        <v>-0.006692444973230227</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.001208370173887463</v>
+        <v>-0.001069682151589202</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.004942290618526146</v>
+        <v>-0.001270310192023627</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.01276156793398178</v>
+        <v>-0.0122932917316693</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.00227769110764432</v>
+        <v>-0.004033419763756862</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.02085854220685679</v>
+        <v>-0.01463555171420344</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.004617784711388473</v>
+        <v>-0.01039001560062406</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.003831417624521116</v>
+        <v>-0.004262877442273471</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.004984154422356657</v>
+        <v>-0.007898614795166481</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.00179781903919839</v>
+        <v>-0.0008923259964307096</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.002349791790600819</v>
+        <v>-0.007991225321215944</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.02518006338231055</v>
+        <v>-0.01898588303082686</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.02947277441659461</v>
+        <v>-0.01696917314894846</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.03595505617977526</v>
+        <v>-0.0124330755502677</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.001344743276283644</v>
+        <v>-0.00198342214328</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.001006512729425679</v>
+        <v>-0.000710479573712186</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.0007400828892835775</v>
+        <v>-0.001065719360568318</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.0177223088923557</v>
+        <v>-0.02440218957072892</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.02633246902909821</v>
+        <v>-0.009997118985883059</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.0008252284114353637</v>
+        <v>-0.001397977394408101</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.009305675597810415</v>
+        <v>-0.004955344281186979</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.01631825273010922</v>
+        <v>-0.009075194468452919</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.0007962253022707588</v>
+        <v>-0.001546698393813195</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.007288965715931994</v>
+        <v>-0.006009473060982773</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.03607029674445402</v>
+        <v>-0.0154134255257851</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.003876886652855827</v>
+        <v>-0.0125741029641186</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.008075449454759843</v>
+        <v>-0.004700720777185852</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.0006778661951076348</v>
+        <v>-0.0008923259964306984</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.003225806451612845</v>
+        <v>-0.004627173592690803</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.002808112324492984</v>
+        <v>-0.004647720544700962</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.001598579040852566</v>
+        <v>-0.002468768590124937</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.002689486552567277</v>
+        <v>-0.00232004759071982</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.004586583463338567</v>
+        <v>-0.003182527301092053</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.002383863080684634</v>
+        <v>-0.01081165778752744</v>
       </c>
       <c r="BX5" t="n">
-        <v>-9.36037441497839e-05</v>
+        <v>-0.0005304212168486977</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.001160023795359877</v>
+        <v>-0.003290504544030104</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.003300913645741277</v>
+        <v>-0.0008288928359975634</v>
       </c>
       <c r="CA5" t="n">
         <v>0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.002505157677571535</v>
+        <v>-0.0008147916013789058</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.005353955978584168</v>
+        <v>-0.005741029641185657</v>
       </c>
       <c r="CD5" t="n">
-        <v>-8.841732979665284e-05</v>
+        <v>-0.0003271861986912317</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.0004759071980963481</v>
+        <v>-0.002298850574712596</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.00232832301797824</v>
+        <v>-0.00692667706708272</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.005978584176085644</v>
+        <v>-0.005750516071955147</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.001622464898595954</v>
+        <v>-0.003093396787626423</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.004045211183819142</v>
+        <v>-0.006677067082683308</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.002903422982885129</v>
+        <v>-0.003071137574428106</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.003256364712847826</v>
+        <v>-0.001405867970660102</v>
       </c>
     </row>
     <row r="6">
@@ -1961,268 +1961,268 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.004844670865885451</v>
+        <v>-0.006530203459275621</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.004569078158267256</v>
+        <v>-0.007050225080295239</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.003944834199569186</v>
+        <v>-0.00383916588658742</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.176453702500966e-05</v>
+        <v>0.001872684269159616</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0006007748340867453</v>
+        <v>-0.003596265720487632</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.002625144671419466</v>
+        <v>-0.002623015208628496</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.093965385618236e-05</v>
+        <v>-8.880337598695388e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.002069474121180343</v>
+        <v>-0.005342071173764879</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003490817430210497</v>
+        <v>0.005354199188337313</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01089133627493663</v>
+        <v>0.01015296531635629</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.003960496086017754</v>
+        <v>-0.006934471918682145</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.004714815313166722</v>
+        <v>-0.005238660957420516</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0047953022995366</v>
+        <v>-0.003914301781542654</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.004448136477843848</v>
+        <v>-0.008292183405123974</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.003766233419208398</v>
+        <v>0.0009791057739175159</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.001056370127665762</v>
+        <v>-0.002342996099379971</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.003059888335096162</v>
+        <v>-0.001355936635872848</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.001857338573072303</v>
+        <v>-0.0007670855709606128</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.003020376138653005</v>
+        <v>-0.003750322432518521</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0001046726533353942</v>
+        <v>0.0001277852238682542</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.002803441448900404</v>
+        <v>-0.004124537594673914</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.003027045041009188</v>
+        <v>-0.003400744656513371</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.0004130743104998474</v>
+        <v>-0.001993310651281871</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0001552920298626997</v>
+        <v>-0.0003444457427310088</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.0002428120758508289</v>
+        <v>0.0006679232084365356</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0001329394387001554</v>
+        <v>-0.0009870702123620317</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.001439706350397538</v>
+        <v>0.00172870431691157</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.004630994657796794</v>
+        <v>-0.007691767829958268</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.003119747112826082</v>
+        <v>-0.001430169647763851</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.002239442108018705</v>
+        <v>-0.009409541490887335</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0003664118168106273</v>
+        <v>-0.0002806346216241401</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0002129666911599826</v>
+        <v>-0.0004541189979221288</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.006592371767388631</v>
+        <v>-0.006583342286031088</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.007585489626481654</v>
+        <v>-0.006547199587764174</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0008110464119604366</v>
+        <v>-0.001592153866042548</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.0007166867281473088</v>
+        <v>-0.0004015994910290838</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0002661936200785226</v>
+        <v>-0.0002116521544422989</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.00307397411349386</v>
+        <v>-0.005305574307191125</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0002216444168364529</v>
+        <v>-0.0005257037984769452</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.000692073581802502</v>
+        <v>0.0004430522803364201</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.004198246169455616</v>
+        <v>-0.007990576764413015</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.001589640462366637</v>
+        <v>-0.001384731429375546</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.01093028581345516</v>
+        <v>-0.005237308113857264</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.0009734120787045054</v>
+        <v>-0.001798388279505031</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.0009474010966979168</v>
+        <v>-0.002526752349785727</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.002012749475496311</v>
+        <v>-0.002695838876250367</v>
       </c>
       <c r="AX6" t="n">
-        <v>-1.382948471465584e-05</v>
+        <v>-0.0004278600205815691</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.001920816158489039</v>
+        <v>-0.001224237288493776</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.002339724990445013</v>
+        <v>-0.00178412140573686</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.003706709733624941</v>
+        <v>-0.006980590262003763</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.01492655129905227</v>
+        <v>-0.005525793755713552</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0006643528782444786</v>
+        <v>-0.0009800541140810137</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0001270487841718348</v>
+        <v>-0.0004656228425176018</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.0002876310723460285</v>
+        <v>-0.001022134473360398</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.005617445068967131</v>
+        <v>-0.00871220839315431</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.003740359496220225</v>
+        <v>-0.004989976009850441</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>5.175112771864942e-05</v>
+        <v>-2.96011253289652e-05</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.00359304366225808</v>
+        <v>-0.001976617134584088</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.004355129330630056</v>
+        <v>-0.002379671149020965</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0004099175202963129</v>
+        <v>-0.001128771309322937</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.00302459706556365</v>
+        <v>-0.002911193288847213</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.009331116919109114</v>
+        <v>-0.007075876015409455</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.001146941654496894</v>
+        <v>-0.001376455613161826</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.002429862545131664</v>
+        <v>-0.001503785570635924</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0.0001093640933901602</v>
+        <v>-0.0003699190084769211</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.001846008460834478</v>
+        <v>-0.001838601430380446</v>
       </c>
       <c r="BS6" t="n">
-        <v>-3.023875773209005e-05</v>
+        <v>-0.001128557489265158</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0008336423344574101</v>
+        <v>-0.001399078710563498</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.0009540968351644003</v>
+        <v>0.001044734496944977</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.002552402579964305</v>
+        <v>-0.001430992057572836</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.0008360199389486483</v>
+        <v>-0.001440884675410048</v>
       </c>
       <c r="BX6" t="n">
-        <v>-5.14372743074698e-05</v>
+        <v>-0.000123486858809263</v>
       </c>
       <c r="BY6" t="n">
-        <v>-1.702670407829622e-05</v>
+        <v>-0.0002195649133077987</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.0005567425864865056</v>
+        <v>-0.000557706031873309</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0001730215726077955</v>
+        <v>-0.0005775572234115623</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.0003336261336776697</v>
+        <v>-0.001553445532868125</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-5.322904515461524e-05</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0003067415483905822</v>
+        <v>-0.0001978794653973714</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.00135212835687685</v>
+        <v>-0.001956557690686309</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.0005406942149128402</v>
+        <v>-0.002300321848046</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0005952894732377423</v>
+        <v>-0.001069148458965882</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.002355621783066919</v>
+        <v>-0.002411806682417539</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.002070039978871982</v>
+        <v>-0.001706654430918797</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.001922509452439525</v>
+        <v>-0.0004371939214767112</v>
       </c>
     </row>
     <row r="7">
@@ -2232,268 +2232,268 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0008635192071070441</v>
+        <v>-0.003303731083839417</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.00157764793825847</v>
+        <v>-0.002593604966386082</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0006214856466410235</v>
+        <v>0.0002387486697511931</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001330472901067614</v>
+        <v>0.002552251158618407</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001912320830514308</v>
+        <v>-0.001201087793526867</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0006436121551213648</v>
+        <v>-8.048161549667476e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001769739680400118</v>
+        <v>4.387751385038774e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0006264234754833342</v>
+        <v>-0.001677330752609213</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01263722756186457</v>
+        <v>0.01736830969630391</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01708913335962658</v>
+        <v>0.01661354359697572</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.002208481563750114</v>
+        <v>-0.0001470675692436307</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.001317220508868638</v>
+        <v>-0.0008949830961449911</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.001387340629027312</v>
+        <v>0.001015131181373619</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0004335321015473182</v>
+        <v>0.003586148708292753</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.00615811576079045</v>
+        <v>0.009685213607549991</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0001577579789678651</v>
+        <v>-0.0006656154647370571</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0002671640766695515</v>
+        <v>-2.824135643683114e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>0.00137362415694709</v>
+        <v>0.0001260029737364055</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.000647616219373981</v>
+        <v>-0.00259950328974326</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0001925741776136469</v>
+        <v>0.0001804969882788443</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0007040883657951967</v>
+        <v>-0.001891900752890718</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.00184974539301288</v>
+        <v>-0.0006662275680497265</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001298636130257763</v>
+        <v>0.0003409639779612894</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0005002466472836309</v>
+        <v>0.0008154674285821173</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001430653136395871</v>
+        <v>0.001679070390901383</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.220446049250313e-17</v>
+        <v>0.0002511701292861879</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.004899562123559371</v>
+        <v>0.002409726772755328</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.003344572492577114</v>
+        <v>-0.002190110016770763</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.002030887377770252</v>
+        <v>0.0003400647757024478</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.0003247403891519729</v>
+        <v>-0.003800427062508238</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.0001636418422670316</v>
+        <v>0.0003391607577740485</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0002955181563421061</v>
+        <v>-6.240249609983927e-05</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.001431489502292777</v>
+        <v>-0.003619541144260436</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.001696481624390578</v>
+        <v>-0.00159383579873214</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.0005035833617253127</v>
+        <v>-0.000900936703359534</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.000201670988187852</v>
+        <v>0.0004449275033594657</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.001778634180390798</v>
+        <v>0.001649156995327006</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.001905431161869559</v>
+        <v>-0.003279562055260849</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.0005157103808439533</v>
+        <v>-0.0002507599904299385</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.002673424166096289</v>
+        <v>0.001743650991828894</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.002850009717940594</v>
+        <v>-0.001887647648317359</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0002162701875242979</v>
+        <v>-0.0002824507296455114</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.004463007462461439</v>
+        <v>-0.003083784652740418</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.001261663019524106</v>
+        <v>0.001979829907462394</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0004702994867353316</v>
+        <v>-0.0009363359890759371</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.0004207374959677934</v>
+        <v>-0.00083734755807639</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0001983097772677855</v>
+        <v>4.87507916844765e-05</v>
       </c>
       <c r="AY7" t="n">
-        <v>2.302073224412225e-05</v>
+        <v>-0.0002592206312846901</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0006054388629644358</v>
+        <v>0.0001367629958023919</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0007101507601988799</v>
+        <v>-0.003551841240878939</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.0007601797230750439</v>
+        <v>-0.001743117298126234</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0001714617413173414</v>
+        <v>-0.0006495602444039905</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.000349689024488592</v>
+        <v>-0.0001662572181359789</v>
       </c>
       <c r="BE7" t="n">
-        <v>-7.338472260489114e-05</v>
+        <v>-0.0002392421594503924</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.002000865397452173</v>
+        <v>-0.001802371840028111</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.0003194839288398365</v>
+        <v>-0.002147424218953786</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.0002615923614732507</v>
+        <v>-1.477104874443858e-05</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0009346634529259212</v>
+        <v>0.0009352961981824504</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.002510544416795518</v>
+        <v>0.0003673870671208501</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0.0002954442303373716</v>
+        <v>-0.0004069112611831127</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.0005025382699207715</v>
+        <v>0.0007281731263939495</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0.0004542136681018716</v>
+        <v>-0.0004698473729138231</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.0002912775903545995</v>
+        <v>0.0002622626666197003</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.0003820293398533182</v>
+        <v>-0.0004297411708683363</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.0001035940825609372</v>
+        <v>-0.0001860893527716401</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0009171792934884404</v>
+        <v>-0.0001217392639033643</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0007249057857922846</v>
+        <v>-0.0005168821630983256</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0.0003018088081531811</v>
+        <v>5.968614695118224e-05</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.005328106188556059</v>
+        <v>0.004488902199768013</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.0002247177937221678</v>
+        <v>-0.001023547564797978</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.0007427897271791329</v>
+        <v>0.001553084631246143</v>
       </c>
       <c r="BX7" t="n">
-        <v>4.424349200999323e-05</v>
+        <v>-7.382929361698375e-05</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0003394555042290748</v>
+        <v>0.0004004351352372481</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0003327177115184821</v>
+        <v>-0.0003396047099040068</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0.0001203138035804352</v>
+        <v>0.000502390318591689</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.001863215213096725</v>
+        <v>-0.0008723183200358587</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-1.473622163277177e-05</v>
       </c>
       <c r="CE7" t="n">
-        <v>6.088023600351878e-05</v>
+        <v>0.0005168050553189585</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.0007733227422006717</v>
+        <v>-0.001003806098852072</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0002219853880711942</v>
+        <v>0.0006061900267662179</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.0001375305623471934</v>
+        <v>-0.0004421979210729732</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0.001240280541581051</v>
+        <v>-0.0007382901516578833</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0.0002754111569365613</v>
+        <v>-0.0005023724717483358</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0.001221094530872263</v>
+        <v>-0.0001626039723538864</v>
       </c>
     </row>
     <row r="8">
@@ -2503,268 +2503,268 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001652894800518587</v>
+        <v>-0.0001219146324338977</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0001236562700401733</v>
+        <v>0.0001673390082089748</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00283530456625205</v>
+        <v>0.001998763577888321</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003338955887916789</v>
+        <v>0.003542481087931465</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003376456723100318</v>
+        <v>7.386835800056168e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001968484690468816</v>
+        <v>0.002375790135306647</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0002830838538911862</v>
+        <v>0.0001825696922459347</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002852840152725913</v>
+        <v>0.001849334450516013</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0212387447527058</v>
+        <v>0.0241498722235717</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02658470995094678</v>
+        <v>0.02683391884446639</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.001022506181586361</v>
+        <v>0.00457163293155646</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.000142368654084804</v>
+        <v>0.002300590661256452</v>
       </c>
       <c r="O8" t="n">
-        <v>0.006163563916393863</v>
+        <v>0.00341925190899352</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01160720229433778</v>
+        <v>0.02046994293775392</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0108526131998825</v>
+        <v>0.01515987515135892</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001802098637121691</v>
+        <v>0.003280224908592385</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002484277774670357</v>
+        <v>0.003754639183122327</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002398268580784346</v>
+        <v>0.001197951089827531</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001476338677988939</v>
+        <v>-0.0005609906824152744</v>
       </c>
       <c r="V8" t="n">
-        <v>0.000236564779959153</v>
+        <v>0.00025839363153628</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003804834632408008</v>
+        <v>0.001614606157279974</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.001124739875844599</v>
+        <v>0.002276935211116965</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.002737706505169238</v>
+        <v>0.003959171867616176</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001821993065697059</v>
+        <v>0.002409672089300752</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003311336816136551</v>
+        <v>0.003713623878584047</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001182823899795543</v>
+        <v>0.0006866197497213483</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.009266521437610892</v>
+        <v>0.00471717374830734</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.0005114719674297524</v>
+        <v>0.003692506336780238</v>
       </c>
       <c r="AE8" t="n">
-        <v>7.321581728305937e-05</v>
+        <v>0.002610525844063061</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.001649634921592755</v>
+        <v>-4.09017703158959e-05</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.000162496840709675</v>
+        <v>0.000729781934339671</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0005844206102043614</v>
+        <v>0.0005923026165564921</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.001810846791682849</v>
+        <v>-0.001804318561965665</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0.0003502266843100288</v>
+        <v>0.003325966241744763</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.0001623900611010087</v>
+        <v>-0.0005004753242148496</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0001721121118433755</v>
+        <v>0.001231638956320405</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0030963488534413</v>
+        <v>0.003198418441345044</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.0006011160544811239</v>
+        <v>0.0006635450056111407</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.001253729821454619</v>
+        <v>0.0001406463580051281</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.004231138794257114</v>
+        <v>0.002861925506215187</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.001599953188539049</v>
+        <v>0.001158672947594372</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.001024076311459577</v>
+        <v>0.002290294619326025</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.001441888348279727</v>
+        <v>0.0003405859147332269</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.00407563997127354</v>
+        <v>0.00364630060358318</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.001979203503857874</v>
+        <v>0.001153190955224412</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.003388716711319589</v>
+        <v>0.001951390582533582</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0006770091028360404</v>
+        <v>0.0003652177917101678</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.002455202366528117</v>
+        <v>0.002238797455655145</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.002475265127004719</v>
+        <v>0.001677415194235049</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.00232974497537361</v>
+        <v>-0.001113042877372186</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.0009071610184796602</v>
+        <v>0.002093591789648599</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0006869542254411942</v>
+        <v>2.360627173439711e-05</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0008980215597198027</v>
+        <v>0.0004707334554636206</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.923259964305764e-05</v>
+        <v>-2.210433244916044e-05</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.00233333814867113</v>
+        <v>0.0009675546360079419</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.001821468152827194</v>
+        <v>-0.001130561322896051</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0008237982942300298</v>
+        <v>0.000242733683023269</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.00227692177184374</v>
+        <v>0.001893989496655191</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.00148962187487828</v>
+        <v>0.001718122129696895</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0001192294275142336</v>
+        <v>-2.340093603744875e-05</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0007432308838279278</v>
+        <v>0.003264270029468233</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.0005179068957765682</v>
+        <v>0.002311770702040172</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0006871014166042217</v>
+        <v>0.001971330926576625</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.00230093847320352</v>
+        <v>0.002115840168422267</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0001721121118433727</v>
+        <v>0.0003610808868641985</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.002534096783264534</v>
+        <v>0.000549743939322167</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.002218806130707082</v>
+        <v>0.001682097814643593</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0002367302082591394</v>
+        <v>0.00068146231284128</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.01190762113243146</v>
+        <v>0.005587692642626257</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.001411015469165497</v>
+        <v>0.002250972004442248</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.004961268610602327</v>
+        <v>0.003179519184886584</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0001236177311150832</v>
+        <v>0.0001635017858884202</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0007103551614786374</v>
+        <v>0.0009611514122132403</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0007033529396871713</v>
+        <v>0.0004874459723596236</v>
       </c>
       <c r="CA8" t="n">
         <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0006699972577928065</v>
+        <v>0.001264059222394023</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.003154602115337923</v>
+        <v>0.001906155140849605</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0003992521432957336</v>
+        <v>0.0008062852965237482</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.001445017435720133</v>
+        <v>-0.00011228571921581</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0006663771665668227</v>
+        <v>0.003096223279089386</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0009174119968201638</v>
+        <v>-0.0001205264370999493</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.001672164293476425</v>
+        <v>0.003370688464863517</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.002438965694654219</v>
+        <v>0.002308426045239467</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.001408218831860497</v>
+        <v>0.001077751671610006</v>
       </c>
     </row>
     <row r="9">
@@ -2774,268 +2774,268 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008463580064877563</v>
+        <v>0.004246534945443858</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01135358301386017</v>
+        <v>0.007342966676496643</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01615089890951954</v>
+        <v>0.009195402298850608</v>
       </c>
       <c r="F9" t="n">
-        <v>0.007231345433592662</v>
+        <v>0.004912696063924238</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009018567639257269</v>
+        <v>0.003684055408193376</v>
       </c>
       <c r="H9" t="n">
-        <v>0.007436049970255809</v>
+        <v>0.01011501032143913</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0004423473901503549</v>
+        <v>0.0005928237129484981</v>
       </c>
       <c r="J9" t="n">
-        <v>0.007102858826996706</v>
+        <v>0.003391329991153103</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03386383731211313</v>
+        <v>0.03150604185086946</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03521956970232829</v>
+        <v>0.03262599469496025</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001916838690651679</v>
+        <v>0.005948505474992594</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01877394636015321</v>
+        <v>0.008649144254278762</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0150398112651135</v>
+        <v>0.01320365458296495</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01796549672813803</v>
+        <v>0.02780031201248048</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02150505651397979</v>
+        <v>0.03289708506841164</v>
       </c>
       <c r="R9" t="n">
-        <v>0.00911235623709814</v>
+        <v>0.005675597810429212</v>
       </c>
       <c r="S9" t="n">
-        <v>0.006133883810085472</v>
+        <v>0.008340701444149745</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01035092892951924</v>
+        <v>0.005397815912636506</v>
       </c>
       <c r="U9" t="n">
-        <v>0.006458271896195767</v>
+        <v>0.008282396088019617</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0006914433880726434</v>
+        <v>0.0004423473901504216</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01515892420537894</v>
+        <v>0.02503686228251257</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003899556868537646</v>
+        <v>0.003774697729283427</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003338257016248136</v>
+        <v>0.004372397382510385</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003374777975133225</v>
+        <v>0.004174067495559553</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.004393984075493906</v>
+        <v>0.009431181844974979</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002938634399308593</v>
+        <v>0.001435257410296387</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.01657328221763487</v>
+        <v>0.01769389560601594</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.004997025580011916</v>
+        <v>0.007634687409968266</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.004313146233382548</v>
+        <v>0.004261615862681245</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.00356826894721316</v>
+        <v>0.00487444608567209</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.002182247124741921</v>
+        <v>0.001189767995240931</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.001037165082108904</v>
+        <v>0.001006512729425735</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.005013270421704475</v>
+        <v>0.004320804971885172</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.006157049375371826</v>
+        <v>0.005837408312958492</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0.0008288928359976855</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.002595104688882288</v>
+        <v>0.001857859038631704</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.007260155574762339</v>
+        <v>0.01101404056162245</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.0008846947803007654</v>
+        <v>0.005090263391535943</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.002427471876850207</v>
+        <v>0.002595104688882377</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.007087294727744197</v>
+        <v>0.009726353361094564</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.005317577548005881</v>
+        <v>0.005652559928973067</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.002477672140593512</v>
+        <v>0.005393457117595079</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.003850855745721238</v>
+        <v>0.00272269902337966</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.00751547303271437</v>
+        <v>0.01314470969643386</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.00864051902093772</v>
+        <v>0.006605721026245981</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.006867969212551795</v>
+        <v>0.006174298375184706</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.002536125036862236</v>
+        <v>0.002371294851794059</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.0040082522841143</v>
+        <v>0.007168352171326576</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.01680920082571508</v>
+        <v>0.007869142351901014</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.003890362511052114</v>
+        <v>0.01095163806552261</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.001358936484490392</v>
+        <v>0.00665877478543947</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0020716188221368</v>
+        <v>0.0009219245174301172</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.002247191011235994</v>
+        <v>0.0008271787296898036</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0004073958006895029</v>
+        <v>0.002919492774992683</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.006925125776857088</v>
+        <v>0.007740029542097559</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.01447602131438721</v>
+        <v>0.00669034931912379</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>5.918910920390541e-05</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.002189570728896595</v>
+        <v>0.001445001474491325</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.003197158081705154</v>
+        <v>0.00445001566906923</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.01105868475375991</v>
+        <v>0.003610535661438275</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001065496709495495</v>
+        <v>0.000235779546124415</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.002901124925991727</v>
+        <v>0.005918910920390641</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.001955990220048875</v>
+        <v>0.00538780343398465</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.01046995835812018</v>
+        <v>0.007260155574762306</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.00864304235090756</v>
+        <v>0.009017574186113486</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.002794583693460129</v>
+        <v>0.001354076634975498</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.008844713339095389</v>
+        <v>0.009997118985883003</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.004782483434168849</v>
+        <v>0.006222990492653379</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.00159824506424322</v>
+        <v>0.001533470952521421</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.0150693010911235</v>
+        <v>0.01604724863151828</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.002679343128781364</v>
+        <v>0.004782483434168805</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.009761132409318741</v>
+        <v>0.009593777009507299</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0005918910920391207</v>
+        <v>0.0002368265245707768</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.003486027081532728</v>
+        <v>0.002679343128781298</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.002536125036862224</v>
+        <v>0.001279251170046791</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.000115240564678798</v>
+        <v>0.0001178897730622186</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.006799193316047281</v>
+        <v>0.003243880861102966</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.005013270421704463</v>
+        <v>0.004113643089671481</v>
       </c>
       <c r="CD9" t="n">
-        <v>8.862629246676468e-05</v>
+        <v>6.240249609983373e-05</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.001613367905502772</v>
+        <v>0.001184132622853806</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.002413036665622104</v>
+        <v>0.009276865456640693</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.008556611927398483</v>
+        <v>0.007634687409968266</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.002270716602771994</v>
+        <v>0.001299852289512549</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.003833677381303391</v>
+        <v>0.008812260536398508</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.01073322932917314</v>
+        <v>0.004884547069271816</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.00315541138307277</v>
+        <v>0.003111495246326668</v>
       </c>
     </row>
   </sheetData>
